--- a/survey_templates/050_government_instrumentality_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/050_government_instrumentality_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Government Instrumentality Feedback Survey</t>
+          <t>Welcome to the Survey!</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>agency</t>
+          <t>agency_satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>agency</t>
+          <t>Are you satisfied with the agency's work?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rating_scale</t>
+          <t>service_rating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Rate the service provided</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Scale 1-5</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>service_comments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments about the service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,20 +611,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rating_scale_service</t>
+          <t>service_interaction_satisfaction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rating_scale_service</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Satisfaction with service interaction</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Scale 1-5</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,17 +638,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>comments_service_interaction</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Comments about service interaction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,20 +661,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments_service</t>
+          <t>follow_up_satisfaction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comments about agency</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Satisfaction with follow-up</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Scale 1-5</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,17 +688,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rating_scale_citizen_interaction</t>
+          <t>comments_follow_up</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rating_scale_citizen_interaction</t>
+          <t>Comments about follow-up</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +711,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>satisfaction_citizen_interaction</t>
+          <t>service_quality</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Comments about service quality</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,20 +734,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comments_citizen_interaction</t>
+          <t>service_interaction_quality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments about service</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Satisfaction with service interaction quality</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Scale 1-5</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,17 +761,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>service_quality</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How would you rate the quality of the service offered</t>
+          <t>Are you satisfied with follow-up?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +784,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>satisfaction_service_quality</t>
+          <t>comments_follow_up_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Comments Follow Up 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,20 +807,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comments_service_quality</t>
+          <t>overall_service_quality</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments about service quality</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Satisfaction with overall service quality</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Scale 1-5</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,17 +834,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>comments_overall_service_quality</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>Comments about overall service quality</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +857,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>satisfaction_follow_up</t>
+          <t>total_service_quality</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Satisfaction with follow-up</t>
+          <t>Comments about total service quality</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +885,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>comments_follow_up</t>
+          <t>average_service_quality</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Comments about follow-up</t>
+          <t>Comments about average service quality</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +903,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>total_service_quality_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Satisfaction with total service quality</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +926,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rating_average</t>
+          <t>comments_total_service_quality</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rating_average</t>
+          <t>Comments Total Service Quality</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +949,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>comments_average</t>
+          <t>follow_up_averag</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Are you satisfied with follow-up quality?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,18 +977,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>overall_service_quality_rating</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>Overall Service Quality Rating</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>comments_average</t>
+          <t>comments_overall_service_quality_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comments about the average</t>
+          <t>Comments Overall Service Quality 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +1018,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>average_service</t>
+          <t>total_service_quality_averag</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>average_service</t>
+          <t>Total Service Quality Averag</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>comments_average_service</t>
+          <t>average_service_averag</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Comments about average service</t>
+          <t>Average Service Averag</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1069,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rating_total</t>
+          <t>overall_service_rating</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rating_total</t>
+          <t>Rating of overall service quality</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>comments_total</t>
+          <t>comments_overall_service</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Comments total</t>
+          <t>Comments Overall Service</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1118,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +1146,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>agency_choices</t>
+          <t>agency_satisfaction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1163,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>agency_choices</t>
+          <t>agency_satisfaction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,109 +1180,109 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rating_scale_service_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rating_scale_service_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rating_scale_service_choices</t>
+          <t>total_service_quality_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rating_scale_citizen_interaction_choices</t>
+          <t>total_service_quality_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rating_scale_citizen_interaction_choices</t>
+          <t>follow_up_averag_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rating_scale_citizen_interaction_choices</t>
+          <t>follow_up_averag_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>service_quality_choices</t>
+          <t>overall_service_rating_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,117 +1299,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>service_quality_choices</t>
+          <t>overall_service_rating_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>average_service_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>average_service_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>rating_total_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>rating_total_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
